--- a/docs/pats.xlsx
+++ b/docs/pats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D822"/>
+  <dimension ref="A1:D824"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18500,6 +18500,50 @@
         </is>
       </c>
     </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>DS918+</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>6.2.4-25556-0</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>https://global.synologydownload.com/download/DSM/release/6.2.4/25556/DSM_DS918%2B_25556.pat</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>00000000000000000000000000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>DS3617xs</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>6.2.4-25556-0</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>https://global.synologydownload.com/download/DSM/release/6.2.4/25556/DSM_DS3617xs_25556.pat</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>00000000000000000000000000000000</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/pats.xlsx
+++ b/docs/pats.xlsx
@@ -15357,17 +15357,17 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>DS3617xsII</t>
+          <t>DS3617xs</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>6.2.4-25556-0</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS3617xsII_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/6.2.4/25556/DSM_DS3617xs_25556.pat</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -15384,12 +15384,12 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xsII_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS3617xsII_90080.pat</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -15406,12 +15406,12 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS3617xsII_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xsII_42218.pat</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -15428,12 +15428,12 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xsII_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS3617xsII_90075.pat</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -15450,12 +15450,12 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xsII_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xsII_86009.pat</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -15472,12 +15472,12 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xsII_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xsII_86003.pat</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -15494,12 +15494,12 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xsII_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xsII_81180.pat</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -15516,12 +15516,12 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xsII_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xsII_72806.pat</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xsII_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xsII_69057.pat</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xsII_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xsII_64570.pat</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -15582,12 +15582,12 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xsII_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xsII_42962.pat</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -15599,17 +15599,17 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>DS418play</t>
+          <t>DS3617xsII</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS418play_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xsII_42661.pat</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -15626,12 +15626,12 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS418play_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS418play_90080.pat</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -15648,12 +15648,12 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS418play_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS418play_42218.pat</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -15670,12 +15670,12 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS418play_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS418play_90075.pat</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -15692,12 +15692,12 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS418play_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS418play_86009.pat</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -15714,12 +15714,12 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS418play_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS418play_86003.pat</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS418play_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS418play_81180.pat</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -15758,12 +15758,12 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS418play_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS418play_72806.pat</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -15780,12 +15780,12 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS418play_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS418play_69057.pat</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS418play_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS418play_64570.pat</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
@@ -15824,12 +15824,12 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS418play_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS418play_42962.pat</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -15841,17 +15841,17 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>DS718+</t>
+          <t>DS418play</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS718%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS418play_42661.pat</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
@@ -15868,12 +15868,12 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS718%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS718%2B_90080.pat</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -15890,12 +15890,12 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS718%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS718%2B_42218.pat</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -15912,12 +15912,12 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS718%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS718%2B_90075.pat</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -15934,12 +15934,12 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS718%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS718%2B_86009.pat</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -15956,12 +15956,12 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS718%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS718%2B_86003.pat</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -15978,12 +15978,12 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS718%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS718%2B_81180.pat</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -16000,12 +16000,12 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS718%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS718%2B_72806.pat</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -16022,12 +16022,12 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS718%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS718%2B_69057.pat</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -16044,12 +16044,12 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS718%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS718%2B_64570.pat</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -16066,12 +16066,12 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS718%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS718%2B_42962.pat</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -16083,17 +16083,17 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>DS918+</t>
+          <t>DS718+</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS918%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS718%2B_42661.pat</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -16110,12 +16110,12 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS918%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS918%2B_90080.pat</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -16132,12 +16132,12 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS918%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS918%2B_42218.pat</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -16154,12 +16154,12 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS918%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS918%2B_90075.pat</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -16176,12 +16176,12 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS918%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS918%2B_86009.pat</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -16198,12 +16198,12 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS918%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS918%2B_86003.pat</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -16220,12 +16220,12 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS918%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS918%2B_81180.pat</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -16242,12 +16242,12 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS918%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS918%2B_72806.pat</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -16264,12 +16264,12 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS918%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS918%2B_69057.pat</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -16286,12 +16286,12 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS918%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS918%2B_64570.pat</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -16308,12 +16308,12 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS918%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS918%2B_42962.pat</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -16325,17 +16325,17 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>FS1018</t>
+          <t>DS918+</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS1018_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS918%2B_42661.pat</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -16347,17 +16347,17 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>FS1018</t>
+          <t>DS918+</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>6.2.4-25556-0</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS1018_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/6.2.4/25556/DSM_DS918%2B_25556.pat</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -16374,12 +16374,12 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS1018_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS1018_90080.pat</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -16396,12 +16396,12 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS1018_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS1018_42218.pat</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
@@ -16418,12 +16418,12 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS1018_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS1018_90075.pat</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -16440,12 +16440,12 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS1018_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS1018_86009.pat</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -16462,12 +16462,12 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS1018_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS1018_86003.pat</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS1018_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS1018_81180.pat</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
@@ -16506,12 +16506,12 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS1018_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS1018_72806.pat</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -16528,12 +16528,12 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS1018_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS1018_69057.pat</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -16550,12 +16550,12 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS1018_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS1018_64570.pat</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -16567,17 +16567,17 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>FS2017</t>
+          <t>FS1018</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS2017_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS1018_42962.pat</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
@@ -16589,17 +16589,17 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>FS2017</t>
+          <t>FS1018</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2017_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS1018_42661.pat</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -16616,12 +16616,12 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS2017_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS2017_90080.pat</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -16638,12 +16638,12 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2017_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2017_42218.pat</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
@@ -16660,12 +16660,12 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2017_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS2017_90075.pat</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -16682,12 +16682,12 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2017_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2017_86009.pat</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
@@ -16704,12 +16704,12 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2017_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2017_86003.pat</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
@@ -16726,12 +16726,12 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2017_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2017_81180.pat</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
@@ -16748,12 +16748,12 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2017_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2017_72806.pat</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
@@ -16770,12 +16770,12 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2017_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2017_69057.pat</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -16792,12 +16792,12 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2017_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2017_64570.pat</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
@@ -16809,17 +16809,17 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>RS18017xs+</t>
+          <t>FS2017</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS18017xs%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2017_42962.pat</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -16831,17 +16831,17 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>RS18017xs+</t>
+          <t>FS2017</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS18017xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2017_42661.pat</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -16858,12 +16858,12 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS18017xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS18017xs%2B_90080.pat</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -16880,12 +16880,12 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS18017xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS18017xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS18017xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS18017xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -16924,12 +16924,12 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS18017xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS18017xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
@@ -16946,12 +16946,12 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS18017xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS18017xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
@@ -16968,12 +16968,12 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS18017xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS18017xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -16990,12 +16990,12 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS18017xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS18017xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -17012,12 +17012,12 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS18017xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS18017xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -17034,12 +17034,12 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS18017xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS18017xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
@@ -17051,17 +17051,17 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>RS2418+</t>
+          <t>RS18017xs+</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS2418%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS18017xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -17073,17 +17073,17 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>RS2418+</t>
+          <t>RS18017xs+</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS18017xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -17100,12 +17100,12 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2418%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS2418%2B_90080.pat</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -17122,12 +17122,12 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418%2B_42218.pat</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
@@ -17144,12 +17144,12 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2418%2B_90075.pat</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
@@ -17166,12 +17166,12 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418%2B_86009.pat</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
@@ -17188,12 +17188,12 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418%2B_86003.pat</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
@@ -17210,12 +17210,12 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418%2B_81180.pat</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
@@ -17232,12 +17232,12 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418%2B_72806.pat</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -17254,12 +17254,12 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418%2B_69057.pat</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
@@ -17276,12 +17276,12 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418%2B_64570.pat</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
@@ -17293,17 +17293,17 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>RS2418RP+</t>
+          <t>RS2418+</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS2418RP%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418%2B_42962.pat</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
@@ -17315,17 +17315,17 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>RS2418RP+</t>
+          <t>RS2418+</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418%2B_42661.pat</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
@@ -17342,12 +17342,12 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2418RP%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS2418RP%2B_90080.pat</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
@@ -17364,12 +17364,12 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
@@ -17386,12 +17386,12 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2418RP%2B_90075.pat</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
@@ -17408,12 +17408,12 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
@@ -17430,12 +17430,12 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
@@ -17452,12 +17452,12 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
@@ -17474,12 +17474,12 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
@@ -17496,12 +17496,12 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -17518,12 +17518,12 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -17535,17 +17535,17 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>RS2818RP+</t>
+          <t>RS2418RP+</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS2818RP%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -17557,17 +17557,17 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>RS2818RP+</t>
+          <t>RS2418RP+</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2818RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2818RP%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS2818RP%2B_90080.pat</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -17606,12 +17606,12 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2818RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2818RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
@@ -17628,12 +17628,12 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2818RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2818RP%2B_90075.pat</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2818RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2818RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -17672,12 +17672,12 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2818RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2818RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -17694,12 +17694,12 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2818RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2818RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -17716,12 +17716,12 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2818RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2818RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
@@ -17738,12 +17738,12 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2818RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2818RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
@@ -17760,12 +17760,12 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2818RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2818RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
@@ -17777,17 +17777,17 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>RS3617RPxs</t>
+          <t>RS2818RP+</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS3617RPxs_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2818RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
@@ -17799,17 +17799,17 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>RS3617RPxs</t>
+          <t>RS2818RP+</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617RPxs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2818RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
@@ -17826,12 +17826,12 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3617RPxs_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS3617RPxs_90080.pat</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617RPxs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617RPxs_42218.pat</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
@@ -17870,12 +17870,12 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617RPxs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3617RPxs_90075.pat</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
@@ -17892,12 +17892,12 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617RPxs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617RPxs_86009.pat</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
@@ -17914,12 +17914,12 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617RPxs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617RPxs_86003.pat</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
@@ -17936,12 +17936,12 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617RPxs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617RPxs_81180.pat</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
@@ -17958,12 +17958,12 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617RPxs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617RPxs_72806.pat</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
@@ -17980,12 +17980,12 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617RPxs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617RPxs_69057.pat</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
@@ -18002,12 +18002,12 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617RPxs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617RPxs_64570.pat</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
@@ -18019,17 +18019,17 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>RS3617xs+</t>
+          <t>RS3617RPxs</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS3617xs%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617RPxs_42962.pat</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
@@ -18041,17 +18041,17 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>RS3617xs+</t>
+          <t>RS3617RPxs</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617RPxs_42661.pat</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
@@ -18068,12 +18068,12 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3617xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS3617xs%2B_90080.pat</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
@@ -18090,12 +18090,12 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -18112,12 +18112,12 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3617xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
@@ -18134,12 +18134,12 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
@@ -18156,12 +18156,12 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
@@ -18178,12 +18178,12 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -18200,12 +18200,12 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
@@ -18222,12 +18222,12 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -18244,12 +18244,12 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -18261,17 +18261,17 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>RS4017xs+</t>
+          <t>RS3617xs+</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS4017xs%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
@@ -18283,17 +18283,17 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>RS4017xs+</t>
+          <t>RS3617xs+</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4017xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -18310,12 +18310,12 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS4017xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS4017xs%2B_90080.pat</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -18332,12 +18332,12 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4017xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4017xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -18354,12 +18354,12 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4017xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS4017xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -18376,12 +18376,12 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4017xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4017xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
@@ -18398,12 +18398,12 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4017xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4017xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -18420,12 +18420,12 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4017xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4017xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -18442,12 +18442,12 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4017xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4017xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -18464,12 +18464,12 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4017xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4017xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -18486,12 +18486,12 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS4017xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4017xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -18503,17 +18503,17 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>DS918+</t>
+          <t>RS4017xs+</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>6.2.4-25556-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/6.2.4/25556/DSM_DS918%2B_25556.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4017xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
@@ -18525,17 +18525,17 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>DS3617xs</t>
+          <t>RS4017xs+</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>6.2.4-25556-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/6.2.4/25556/DSM_DS3617xs_25556.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS4017xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">

--- a/docs/pats.xlsx
+++ b/docs/pats.xlsx
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DS1019+</t>
+          <t>DS1525neo+</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1019%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1525neo%2B_90080.pat</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -485,17 +485,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DS1019+</t>
+          <t>DS1825neo+</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1019%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1825neo%2B_90080.pat</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -507,17 +507,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DS1019+</t>
+          <t>DS725neo+</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1019%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS725neo%2B_90080.pat</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -529,17 +529,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DS1019+</t>
+          <t>DS925neo+</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1019%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS925neo%2B_90080.pat</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -551,17 +551,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DS1019+</t>
+          <t>FS6420</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1019%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS6420_90080.pat</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -573,17 +573,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DS1019+</t>
+          <t>FS6420</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1019%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6420_86009.pat</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -595,17 +595,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DS1019+</t>
+          <t>RS11626xs+</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1019%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS11626xs%2B_90080.pat</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1019%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1019%2B_90080.pat</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1019%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1019%2B_42218.pat</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1019%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1019%2B_90075.pat</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1019%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1019%2B_86009.pat</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -705,17 +705,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DS1520+</t>
+          <t>DS1019+</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1520%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1019%2B_86003.pat</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -727,17 +727,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DS1520+</t>
+          <t>DS1019+</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1520%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1019%2B_81180.pat</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -749,17 +749,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DS1520+</t>
+          <t>DS1019+</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1520%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1019%2B_72806.pat</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -771,17 +771,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DS1520+</t>
+          <t>DS1019+</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1520%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1019%2B_69057.pat</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -793,17 +793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DS1520+</t>
+          <t>DS1019+</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1520%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1019%2B_64570.pat</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -815,17 +815,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DS1520+</t>
+          <t>DS1019+</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1520%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1019%2B_42962.pat</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -837,17 +837,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DS1520+</t>
+          <t>DS1019+</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1520%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1019%2B_42661.pat</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1520%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1520%2B_90080.pat</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1520%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1520%2B_42218.pat</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1520%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1520%2B_90075.pat</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1520%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1520%2B_86009.pat</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -947,17 +947,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DS1522+</t>
+          <t>DS1520+</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1522%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1520%2B_86003.pat</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -969,17 +969,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DS1522+</t>
+          <t>DS1520+</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1522%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1520%2B_81180.pat</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -991,17 +991,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DS1522+</t>
+          <t>DS1520+</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1522%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1520%2B_72806.pat</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1013,17 +1013,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DS1522+</t>
+          <t>DS1520+</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1522%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1520%2B_69057.pat</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1035,17 +1035,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DS1522+</t>
+          <t>DS1520+</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1522%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1520%2B_64570.pat</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1057,17 +1057,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DS1522+</t>
+          <t>DS1520+</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1522%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1520%2B_42962.pat</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1079,17 +1079,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DS1522+</t>
+          <t>DS1520+</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1522%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1520%2B_42661.pat</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1522%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1522%2B_90080.pat</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1522%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1522%2B_90075.pat</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1145,17 +1145,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DS1525+</t>
+          <t>DS1522+</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1525%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1522%2B_86009.pat</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1167,17 +1167,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DS1525+</t>
+          <t>DS1522+</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1525%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1522%2B_86003.pat</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1189,17 +1189,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DS1525+</t>
+          <t>DS1522+</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1525%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1522%2B_81180.pat</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1211,17 +1211,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DS1525+</t>
+          <t>DS1522+</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1525%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1522%2B_72806.pat</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DS1525+</t>
+          <t>DS1522+</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1525%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1522%2B_69057.pat</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1255,17 +1255,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DS1525+</t>
+          <t>DS1522+</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1525%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1522%2B_64570.pat</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1277,17 +1277,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DS1525neo+</t>
+          <t>DS1522+</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1525neo%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1522%2B_42962.pat</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DS1621+</t>
+          <t>DS1525+</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1621%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1525%2B_90080.pat</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1321,17 +1321,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DS1621+</t>
+          <t>DS1525+</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1525%2B_90075.pat</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1343,17 +1343,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DS1621+</t>
+          <t>DS1525+</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1621%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1525%2B_86009.pat</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1365,17 +1365,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DS1621+</t>
+          <t>DS1525+</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1525%2B_86003.pat</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1387,17 +1387,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DS1621+</t>
+          <t>DS1525+</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1525%2B_81180.pat</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1409,17 +1409,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DS1621+</t>
+          <t>DS1525+</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1525%2B_72806.pat</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1621%2B_90080.pat</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621%2B_42218.pat</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1621%2B_90075.pat</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621%2B_86009.pat</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621%2B_86003.pat</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1541,17 +1541,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DS1621xs+</t>
+          <t>DS1621+</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1621xs%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621%2B_81180.pat</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1563,17 +1563,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DS1621xs+</t>
+          <t>DS1621+</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621%2B_72806.pat</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1585,17 +1585,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DS1621xs+</t>
+          <t>DS1621+</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1621xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621%2B_69057.pat</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1607,17 +1607,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DS1621xs+</t>
+          <t>DS1621+</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621%2B_64570.pat</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1629,17 +1629,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DS1621xs+</t>
+          <t>DS1621+</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621%2B_42962.pat</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1651,17 +1651,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DS1621xs+</t>
+          <t>DS1621+</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621%2B_42661.pat</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1621xs%2B_90080.pat</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1621xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1783,17 +1783,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DS1819+</t>
+          <t>DS1621xs+</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1819%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1805,17 +1805,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DS1819+</t>
+          <t>DS1621xs+</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1819%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1827,17 +1827,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DS1819+</t>
+          <t>DS1621xs+</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1819%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1849,17 +1849,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DS1819+</t>
+          <t>DS1621xs+</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1819%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1871,17 +1871,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DS1819+</t>
+          <t>DS1621xs+</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1819%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1893,17 +1893,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DS1819+</t>
+          <t>DS1621xs+</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1819%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1819%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1819%2B_90080.pat</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1819%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1819%2B_42218.pat</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1819%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1819%2B_90075.pat</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1819%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1819%2B_86009.pat</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1819%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1819%2B_86003.pat</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2025,17 +2025,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DS1821+</t>
+          <t>DS1819+</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1821%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1819%2B_81180.pat</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2047,17 +2047,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DS1821+</t>
+          <t>DS1819+</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1821%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1819%2B_72806.pat</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2069,17 +2069,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DS1821+</t>
+          <t>DS1819+</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1821%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1819%2B_69057.pat</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2091,17 +2091,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DS1821+</t>
+          <t>DS1819+</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1821%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1819%2B_64570.pat</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2113,17 +2113,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DS1821+</t>
+          <t>DS1819+</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1821%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1819%2B_42962.pat</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2135,17 +2135,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DS1821+</t>
+          <t>DS1819+</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1821%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1819%2B_42661.pat</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1821%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1821%2B_90080.pat</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1821%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1821%2B_42218.pat</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1821%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1821%2B_90075.pat</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1821%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1821%2B_86009.pat</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1821%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1821%2B_86003.pat</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2267,17 +2267,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DS1823xs+</t>
+          <t>DS1821+</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1823xs%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1821%2B_81180.pat</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2289,17 +2289,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DS1823xs+</t>
+          <t>DS1821+</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1823xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1821%2B_72806.pat</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2311,17 +2311,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DS1823xs+</t>
+          <t>DS1821+</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1823xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1821%2B_69057.pat</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2333,17 +2333,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DS1823xs+</t>
+          <t>DS1821+</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1823xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1821%2B_64570.pat</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2355,17 +2355,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DS1823xs+</t>
+          <t>DS1821+</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1823xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1821%2B_42962.pat</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2377,17 +2377,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DS1823xs+</t>
+          <t>DS1821+</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1823xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1821%2B_42661.pat</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1823xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1823xs%2B_90080.pat</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1823xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1823xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS1823xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1823xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2465,17 +2465,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DS1825+</t>
+          <t>DS1823xs+</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1825%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1823xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2487,17 +2487,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DS1825+</t>
+          <t>DS1823xs+</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1825%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1823xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2509,17 +2509,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DS1825+</t>
+          <t>DS1823xs+</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1825%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1823xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2531,17 +2531,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DS1825+</t>
+          <t>DS1823xs+</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1825%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1823xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2553,17 +2553,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DS1825+</t>
+          <t>DS1823xs+</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1825%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1823xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2575,17 +2575,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DS1825+</t>
+          <t>DS1823xs+</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1825%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS1823xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2597,7 +2597,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DS1825neo+</t>
+          <t>DS1825+</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1825neo%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS1825%2B_90080.pat</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2619,17 +2619,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DS220+</t>
+          <t>DS1825+</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS220%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1825%2B_90075.pat</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2641,17 +2641,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DS220+</t>
+          <t>DS1825+</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS220%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1825%2B_86009.pat</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2663,17 +2663,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DS220+</t>
+          <t>DS1825+</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS220%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1825%2B_86003.pat</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2685,17 +2685,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DS220+</t>
+          <t>DS1825+</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS220%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1825%2B_81180.pat</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2707,17 +2707,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DS220+</t>
+          <t>DS1825+</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS220%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1825%2B_72806.pat</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS220%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS220%2B_90080.pat</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS220%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS220%2B_42218.pat</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS220%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS220%2B_90075.pat</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS220%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS220%2B_86009.pat</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS220%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS220%2B_86003.pat</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS220%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS220%2B_81180.pat</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2861,17 +2861,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DS224+</t>
+          <t>DS220+</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS224%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS220%2B_72806.pat</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2883,17 +2883,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DS224+</t>
+          <t>DS220+</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS224%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS220%2B_69057.pat</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2905,17 +2905,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DS224+</t>
+          <t>DS220+</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS224%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS220%2B_64570.pat</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2927,17 +2927,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DS224+</t>
+          <t>DS220+</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS224%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS220%2B_42962.pat</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2949,17 +2949,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DS224+</t>
+          <t>DS220+</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS224%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS220%2B_42661.pat</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS224%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS224%2B_90080.pat</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS224%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS224%2B_90075.pat</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3015,17 +3015,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DS225+</t>
+          <t>DS224+</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS225%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS224%2B_86009.pat</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3037,17 +3037,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DS225+</t>
+          <t>DS224+</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS225%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS224%2B_86003.pat</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3059,17 +3059,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DS225+</t>
+          <t>DS224+</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS225%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS224%2B_81180.pat</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3081,17 +3081,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DS225+</t>
+          <t>DS224+</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS225%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS224%2B_72806.pat</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3103,17 +3103,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DS225+</t>
+          <t>DS224+</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS225%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS224%2B_69057.pat</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS225%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS225%2B_90080.pat</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3147,17 +3147,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DS2419+</t>
+          <t>DS225+</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS2419%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS225%2B_90075.pat</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3169,17 +3169,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DS2419+</t>
+          <t>DS225+</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS225%2B_86009.pat</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3191,17 +3191,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DS2419+</t>
+          <t>DS225+</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS2419%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS225%2B_86003.pat</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3213,17 +3213,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DS2419+</t>
+          <t>DS225+</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS225%2B_81180.pat</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3235,17 +3235,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DS2419+</t>
+          <t>DS225+</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS225%2B_72806.pat</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS2419%2B_90080.pat</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2B_42218.pat</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS2419%2B_90075.pat</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2B_86009.pat</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2B_86003.pat</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2B_81180.pat</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3389,17 +3389,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DS2419+II</t>
+          <t>DS2419+</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS2419%2BII_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2B_72806.pat</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3411,17 +3411,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DS2419+II</t>
+          <t>DS2419+</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2BII_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2B_69057.pat</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3433,17 +3433,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DS2419+II</t>
+          <t>DS2419+</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS2419%2BII_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2B_64570.pat</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3455,17 +3455,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DS2419+II</t>
+          <t>DS2419+</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2BII_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2B_42962.pat</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3477,17 +3477,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DS2419+II</t>
+          <t>DS2419+</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2BII_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2B_42661.pat</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2BII_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS2419%2BII_90080.pat</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2BII_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2BII_42218.pat</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2BII_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS2419%2BII_90075.pat</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2BII_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2BII_86009.pat</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2BII_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2BII_86003.pat</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2BII_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2BII_81180.pat</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3631,17 +3631,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DS2422+</t>
+          <t>DS2419+II</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS2422%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2BII_72806.pat</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3653,17 +3653,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DS2422+</t>
+          <t>DS2419+II</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS2422%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2BII_69057.pat</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3675,17 +3675,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DS2422+</t>
+          <t>DS2419+II</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2422%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2BII_64570.pat</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3697,17 +3697,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DS2422+</t>
+          <t>DS2419+II</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2422%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2BII_42962.pat</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3719,17 +3719,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DS2422+</t>
+          <t>DS2419+II</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2422%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2BII_42661.pat</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2422%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS2422%2B_90080.pat</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2422%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS2422%2B_90075.pat</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3790,12 +3790,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2422%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2422%2B_86009.pat</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2422%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2422%2B_86003.pat</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2422%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2422%2B_81180.pat</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2422%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2422%2B_72806.pat</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3873,17 +3873,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DS3622xs+</t>
+          <t>DS2422+</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS3622xs%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2422%2B_69057.pat</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3895,17 +3895,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DS3622xs+</t>
+          <t>DS2422+</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS3622xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2422%2B_64570.pat</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3917,17 +3917,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DS3622xs+</t>
+          <t>DS2422+</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3622xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2422%2B_42962.pat</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3939,17 +3939,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DS3622xs+</t>
+          <t>DS2422+</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3622xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2422%2B_42661.pat</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3961,17 +3961,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DS3622xs+</t>
+          <t>DS2422+</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3622xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2422%2B_42218.pat</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3622xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS3622xs%2B_90080.pat</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3622xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS3622xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3622xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3622xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3622xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3622xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3622xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3622xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4098,12 +4098,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3622xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3622xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4115,17 +4115,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>DS420+</t>
+          <t>DS3622xs+</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS420%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3622xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4137,17 +4137,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DS420+</t>
+          <t>DS3622xs+</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS420%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3622xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4159,17 +4159,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>DS420+</t>
+          <t>DS3622xs+</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS420%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3622xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4181,17 +4181,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DS420+</t>
+          <t>DS3622xs+</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS420%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3622xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4203,17 +4203,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DS420+</t>
+          <t>DS3622xs+</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS420%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3622xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS420%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS420%2B_90080.pat</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS420%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS420%2B_42218.pat</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS420%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS420%2B_90075.pat</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS420%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS420%2B_86009.pat</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS420%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS420%2B_86003.pat</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS420%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS420%2B_81180.pat</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4357,17 +4357,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DS423+</t>
+          <t>DS420+</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS423%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS420%2B_72806.pat</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4379,17 +4379,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DS423+</t>
+          <t>DS420+</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS423%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS420%2B_69057.pat</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4401,17 +4401,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DS423+</t>
+          <t>DS420+</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS423%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS420%2B_64570.pat</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4423,17 +4423,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DS423+</t>
+          <t>DS420+</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS423%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS420%2B_42962.pat</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4445,17 +4445,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DS423+</t>
+          <t>DS420+</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS423%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS420%2B_42661.pat</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4472,12 +4472,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS423%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS423%2B_90080.pat</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS423%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS423%2B_90075.pat</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS423%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS423%2B_86009.pat</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS423%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS423%2B_86003.pat</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4555,17 +4555,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DS425+</t>
+          <t>DS423+</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS425%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS423%2B_81180.pat</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4577,17 +4577,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DS425+</t>
+          <t>DS423+</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS425%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS423%2B_72806.pat</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4599,17 +4599,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>DS425+</t>
+          <t>DS423+</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS425%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS423%2B_69057.pat</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4621,17 +4621,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DS425+</t>
+          <t>DS423+</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS425%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS423%2B_64570.pat</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4643,17 +4643,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>DS425+</t>
+          <t>DS423+</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS425%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS423%2B_42962.pat</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS425%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS425%2B_90080.pat</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4687,17 +4687,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DS620slim</t>
+          <t>DS425+</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS620slim_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS425%2B_90075.pat</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4709,17 +4709,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DS620slim</t>
+          <t>DS425+</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS620slim_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS425%2B_86009.pat</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4731,17 +4731,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>DS620slim</t>
+          <t>DS425+</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS620slim_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS425%2B_86003.pat</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4753,17 +4753,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DS620slim</t>
+          <t>DS425+</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS620slim_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS425%2B_81180.pat</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4775,17 +4775,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>DS620slim</t>
+          <t>DS425+</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS620slim_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS425%2B_72806.pat</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS620slim_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS620slim_90080.pat</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS620slim_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS620slim_42218.pat</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_DS620slim_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS620slim_90075.pat</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS620slim_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS620slim_86009.pat</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS620slim_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS620slim_86003.pat</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS620slim_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS620slim_81180.pat</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -4929,17 +4929,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>DS720+</t>
+          <t>DS620slim</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS720%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS620slim_72806.pat</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4951,17 +4951,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>DS720+</t>
+          <t>DS620slim</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS720%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_DS620slim_69057.pat</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4973,17 +4973,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>DS720+</t>
+          <t>DS620slim</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS720%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS620slim_64570.pat</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -4995,17 +4995,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>DS720+</t>
+          <t>DS620slim</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS720%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS620slim_42962.pat</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -5017,17 +5017,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>DS720+</t>
+          <t>DS620slim</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS720%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS620slim_42661.pat</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5044,12 +5044,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS720%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS720%2B_90080.pat</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS720%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS720%2B_42218.pat</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS720%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS720%2B_90075.pat</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS720%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS720%2B_86009.pat</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS720%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS720%2B_86003.pat</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS720%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS720%2B_81180.pat</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -5171,17 +5171,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>DS723+</t>
+          <t>DS720+</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS723%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS720%2B_72806.pat</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5193,17 +5193,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>DS723+</t>
+          <t>DS720+</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS723%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS720%2B_69057.pat</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5215,17 +5215,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>DS723+</t>
+          <t>DS720+</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS723%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS720%2B_64570.pat</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5237,17 +5237,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>DS723+</t>
+          <t>DS720+</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS723%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS720%2B_42962.pat</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5259,17 +5259,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>DS723+</t>
+          <t>DS720+</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS723%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS720%2B_42661.pat</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS723%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS723%2B_90080.pat</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS723%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS723%2B_90075.pat</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS723%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS723%2B_86009.pat</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS723%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS723%2B_86003.pat</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -5369,17 +5369,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>DS725+</t>
+          <t>DS723+</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS725%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS723%2B_81180.pat</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -5391,17 +5391,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>DS725+</t>
+          <t>DS723+</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS725%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS723%2B_72806.pat</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -5413,17 +5413,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>DS725+</t>
+          <t>DS723+</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS725%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS723%2B_69057.pat</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5435,17 +5435,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>DS725+</t>
+          <t>DS723+</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS725%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS723%2B_64570.pat</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -5457,17 +5457,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>DS725+</t>
+          <t>DS723+</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS725%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS723%2B_42962.pat</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS725%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS725%2B_90080.pat</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5501,17 +5501,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>DS725neo+</t>
+          <t>DS725+</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS725neo%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS725%2B_90075.pat</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -5523,17 +5523,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>DS920+</t>
+          <t>DS725+</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS920%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS725%2B_86009.pat</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -5545,17 +5545,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>DS920+</t>
+          <t>DS725+</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS920%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS725%2B_86003.pat</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5567,17 +5567,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>DS920+</t>
+          <t>DS725+</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS920%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS725%2B_81180.pat</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -5589,17 +5589,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>DS920+</t>
+          <t>DS725+</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS920%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS725%2B_72806.pat</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS920%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS920%2B_90080.pat</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS920%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS920%2B_42218.pat</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -5660,12 +5660,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS920%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS920%2B_90075.pat</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS920%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS920%2B_86009.pat</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS920%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS920%2B_86003.pat</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS920%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS920%2B_81180.pat</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS920%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS920%2B_72806.pat</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -5765,17 +5765,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>DS923+</t>
+          <t>DS920+</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS923%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS920%2B_69057.pat</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -5787,17 +5787,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>DS923+</t>
+          <t>DS920+</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS923%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS920%2B_64570.pat</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -5809,17 +5809,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>DS923+</t>
+          <t>DS920+</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS923%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS920%2B_42962.pat</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -5831,17 +5831,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>DS923+</t>
+          <t>DS920+</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS923%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS920%2B_42661.pat</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS923%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS923%2B_90080.pat</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS923%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS923%2B_90075.pat</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS923%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS923%2B_86009.pat</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS923%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS923%2B_86003.pat</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS923%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS923%2B_81180.pat</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -5963,17 +5963,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>DS925+</t>
+          <t>DS923+</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS925%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS923%2B_72806.pat</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -5985,17 +5985,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>DS925+</t>
+          <t>DS923+</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS925%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS923%2B_69057.pat</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -6007,17 +6007,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>DS925+</t>
+          <t>DS923+</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS925%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS923%2B_64570.pat</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -6029,17 +6029,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>DS925+</t>
+          <t>DS923+</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS925%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS923%2B_42962.pat</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS925%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS925%2B_90080.pat</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS925%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS925%2B_90075.pat</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -6095,17 +6095,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>DS925neo+</t>
+          <t>DS925+</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS925neo%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS925%2B_86009.pat</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6117,17 +6117,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>DVA1622</t>
+          <t>DS925+</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA1622_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS925%2B_86003.pat</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -6139,17 +6139,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>DVA1622</t>
+          <t>DS925+</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DVA1622_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS925%2B_81180.pat</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -6161,17 +6161,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>DVA1622</t>
+          <t>DS925+</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA1622_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS925%2B_72806.pat</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -6188,12 +6188,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA1622_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA1622_90080.pat</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA1622_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DVA1622_90075.pat</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA1622_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA1622_86009.pat</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA1622_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA1622_86003.pat</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA1622_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA1622_81180.pat</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA1622_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA1622_72806.pat</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -6315,17 +6315,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>DVA3219</t>
+          <t>DVA1622</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA3219_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA1622_69057.pat</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -6337,17 +6337,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>DVA3219</t>
+          <t>DVA1622</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3219_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA1622_64570.pat</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -6359,17 +6359,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>DVA3219</t>
+          <t>DVA1622</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DVA3219_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA1622_42962.pat</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3219_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA3219_90080.pat</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3219_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3219_42218.pat</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3219_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DVA3219_90075.pat</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3219_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3219_86009.pat</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3219_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3219_86003.pat</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3219_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3219_81180.pat</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3219_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3219_72806.pat</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3219_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3219_69057.pat</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6557,17 +6557,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>DVA3221</t>
+          <t>DVA3219</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA3221_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3219_64570.pat</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -6579,17 +6579,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>DVA3221</t>
+          <t>DVA3219</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3221_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3219_42962.pat</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -6601,17 +6601,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>DVA3221</t>
+          <t>DVA3219</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DVA3221_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3219_42661.pat</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3221_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA3221_90080.pat</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3221_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3221_42218.pat</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3221_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DVA3221_90075.pat</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3221_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3221_86009.pat</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3221_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3221_86003.pat</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3221_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3221_81180.pat</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3221_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3221_72806.pat</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3221_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3221_69057.pat</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -6799,17 +6799,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>DVA7400</t>
+          <t>DVA3221</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA7400_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3221_64570.pat</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6821,17 +6821,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>FS200T</t>
+          <t>DVA3221</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS200T_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3221_42962.pat</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6843,17 +6843,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>FS200T</t>
+          <t>DVA3221</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS200T_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3221_42661.pat</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -6865,17 +6865,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>FS200T</t>
+          <t>DVA7400</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS200T_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA7400_90080.pat</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -6887,7 +6887,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>FS2500</t>
+          <t>FS200T</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS2500_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS200T_90080.pat</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6909,7 +6909,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>FS2500</t>
+          <t>FS200T</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS2500_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS200T_90075.pat</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -6931,7 +6931,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>FS2500</t>
+          <t>FS200T</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2500_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS200T_86009.pat</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2500_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS2500_90080.pat</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2500_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS2500_90075.pat</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2500_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2500_86009.pat</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2500_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2500_86003.pat</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2500_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2500_81180.pat</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2500_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2500_72806.pat</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2500_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2500_69057.pat</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2500_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2500_64570.pat</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -7129,17 +7129,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>FS3400</t>
+          <t>FS2500</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3400_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2500_42962.pat</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -7151,17 +7151,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>FS3400</t>
+          <t>FS2500</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2500_42661.pat</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -7173,17 +7173,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>FS3400</t>
+          <t>FS2500</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3400_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2500_42218.pat</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -7200,12 +7200,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3400_90080.pat</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3400_42218.pat</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3400_90075.pat</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3400_86009.pat</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3400_86003.pat</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3400_81180.pat</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7332,12 +7332,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3400_72806.pat</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3400_69057.pat</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -7371,17 +7371,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>FS3410</t>
+          <t>FS3400</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3410_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3400_64570.pat</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -7393,17 +7393,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>FS3410</t>
+          <t>FS3400</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3410_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3400_42962.pat</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -7415,17 +7415,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>FS3410</t>
+          <t>FS3400</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3410_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3400_42661.pat</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3410_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3410_90080.pat</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3410_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3410_90075.pat</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3410_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3410_86009.pat</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3410_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3410_86003.pat</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3410_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3410_81180.pat</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3410_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3410_72806.pat</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -7569,17 +7569,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>FS3420</t>
+          <t>FS3410</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3420_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3410_69057.pat</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -7591,17 +7591,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>FS3420</t>
+          <t>FS3410</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3420_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3410_64570.pat</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -7613,17 +7613,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>FS3420</t>
+          <t>FS3410</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3420_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3410_42962.pat</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -7635,7 +7635,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>FS3600</t>
+          <t>FS3420</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3600_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3420_90080.pat</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -7657,17 +7657,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>FS3600</t>
+          <t>FS3420</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3600_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3420_90075.pat</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -7679,17 +7679,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>FS3600</t>
+          <t>FS3420</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3600_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3420_86009.pat</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3600_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3600_90080.pat</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3600_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3600_42218.pat</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3600_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3600_90075.pat</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3600_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3600_86009.pat</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -7794,12 +7794,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3600_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3600_86003.pat</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3600_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3600_81180.pat</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3600_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3600_72806.pat</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3600_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3600_69057.pat</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -7877,17 +7877,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>FS6400</t>
+          <t>FS3600</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS6400_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3600_64570.pat</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -7899,17 +7899,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>FS6400</t>
+          <t>FS3600</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS6400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3600_42962.pat</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -7921,17 +7921,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>FS6400</t>
+          <t>FS3600</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS6400_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3600_42661.pat</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS6400_90080.pat</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS6400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS6400_42218.pat</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS6400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS6400_90075.pat</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS6400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6400_86009.pat</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_FS6400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS6400_86003.pat</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS6400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS6400_81180.pat</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS6400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS6400_72806.pat</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS6400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_FS6400_69057.pat</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -8119,17 +8119,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>FS6420</t>
+          <t>FS6400</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS6420_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS6400_64570.pat</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -8141,17 +8141,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>FS6420</t>
+          <t>FS6400</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6420_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS6400_42962.pat</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -8163,17 +8163,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>HD6500</t>
+          <t>FS6400</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_HD6500_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS6400_42661.pat</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_HD6500_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_HD6500_90080.pat</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_HD6500_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_HD6500_90075.pat</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_HD6500_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_HD6500_86009.pat</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_HD6500_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_HD6500_86003.pat</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_HD6500_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_HD6500_81180.pat</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_HD6500_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_HD6500_72806.pat</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_HD6500_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_HD6500_69057.pat</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -8344,12 +8344,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_HD6500_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_HD6500_64570.pat</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -8361,17 +8361,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>RS11626xs+</t>
+          <t>HD6500</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_RS11626xs%2B_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_HD6500_42962.pat</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
